--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Влад/Лаба 1 - Влад.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Влад/Лаба 1 - Влад.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\Влад\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\Влад\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277C332E-0E99-4F66-B399-06594EE9D044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,9 +18,8 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="257">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -2252,21 +2250,35 @@
       <t>погл СО с уч к.д.</t>
     </r>
   </si>
+  <si>
+    <t>Коэффициенты загрязнения в норме, никакие нормы предпринимать не требуется.</t>
+  </si>
+  <si>
+    <t>За счёт относительно небольшого количества машин на исследуемой территории сумма экономического ущерба находится в пределах нормы. Никаких мер предпринимать не требуется.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2522,6 +2534,33 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2537,7 +2576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -2935,356 +2974,559 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3323,7 +3565,7 @@
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8082450-F78B-CDDE-5219-63634BB0070C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B8082450-F78B-CDDE-5219-63634BB0070C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3352,193 +3594,9 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>160812</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>681579</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>34845</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5FE3595-06C9-4D79-B5AC-CCE030669522}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10695462" y="24022051"/>
-          <a:ext cx="6083367" cy="606344"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>16454</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>72736</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>175018</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{350DA055-904D-4D38-A91B-85A34BAF839D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="57150" y="12922829"/>
-          <a:ext cx="4397086" cy="539564"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>95252</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>609601</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2AF4CD5-F473-4644-81D1-977BAEFCC7A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="95252" y="15201900"/>
-          <a:ext cx="3857624" cy="2983706"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>160812</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>681579</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>34846</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD15347C-6BE7-4C43-AC9D-A1C43AE5FA58}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10695462" y="24022051"/>
-          <a:ext cx="6083367" cy="606345"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Лист1"/>
       <sheetName val="Лист2"/>
@@ -3562,117 +3620,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Лист1"/>
-      <sheetName val="Лист2"/>
-      <sheetName val="Лист3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="33">
-          <cell r="J33">
-            <v>2617510.5</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35">
-            <v>10513.2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37">
-            <v>126202.8</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39">
-            <v>4637.8500000000004</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43">
-            <v>230523</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="J45">
-            <v>12375</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="J47">
-            <v>376.68</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="J49">
-            <v>1.5767999999999999E-3</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="J68">
-            <v>0.04</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="J69">
-            <v>0.05</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="J70">
-            <v>2.9999999999999997E-4</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="J71">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="J74">
-            <v>5.0000000000000001E-3</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="J78">
-            <v>0.05</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="J81">
-            <v>9.9999999999999995E-7</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="J84">
-            <v>0.15</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="J85">
-            <v>0.06</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3940,7 +3887,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4135,16 +4082,16 @@
         <v>25</v>
       </c>
       <c r="M8" s="4"/>
-      <c r="R8" s="107" t="s">
+      <c r="R8" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="S8" s="108"/>
-      <c r="T8" s="109"/>
+      <c r="S8" s="94"/>
+      <c r="T8" s="95"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="R9" s="110"/>
-      <c r="S9" s="111"/>
-      <c r="T9" s="112"/>
+      <c r="R9" s="96"/>
+      <c r="S9" s="97"/>
+      <c r="T9" s="98"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -4154,16 +4101,16 @@
         <f>E2-E3</f>
         <v>4.4000000000000021</v>
       </c>
-      <c r="R10" s="113" t="s">
+      <c r="R10" s="84" t="s">
         <v>235</v>
       </c>
-      <c r="S10" s="114"/>
-      <c r="T10" s="115"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="86"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R11" s="116"/>
-      <c r="S11" s="106"/>
-      <c r="T11" s="117"/>
+      <c r="R11" s="87"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="89"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -4173,9 +4120,9 @@
         <f>B2*B10/100</f>
         <v>555.03360000000021</v>
       </c>
-      <c r="R12" s="116"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="117"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="89"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -4185,14 +4132,14 @@
         <f>B12*E1</f>
         <v>66604.032000000021</v>
       </c>
-      <c r="R13" s="116"/>
-      <c r="S13" s="106"/>
-      <c r="T13" s="117"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="89"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R14" s="116"/>
-      <c r="S14" s="106"/>
-      <c r="T14" s="117"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="89"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -4212,14 +4159,14 @@
       <c r="G15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="R15" s="116"/>
-      <c r="S15" s="106"/>
-      <c r="T15" s="117"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="89"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R16" s="116"/>
-      <c r="S16" s="106"/>
-      <c r="T16" s="117"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="89"/>
     </row>
     <row r="17" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -4229,9 +4176,9 @@
         <f>B2*E4/100</f>
         <v>4.7934719999999995</v>
       </c>
-      <c r="R17" s="118"/>
-      <c r="S17" s="119"/>
-      <c r="T17" s="120"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="92"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -4262,7 +4209,7 @@
         <f>E5-E4</f>
         <v>3.9620000000000002</v>
       </c>
-      <c r="R22" s="121"/>
+      <c r="R22" s="74"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -4360,7 +4307,7 @@
       <c r="A34" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="104">
+      <c r="B34" s="72">
         <f>(B32/B15)</f>
         <v>8.0880747652462698E-2</v>
       </c>
@@ -4369,7 +4316,7 @@
       <c r="A36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="105">
+      <c r="B36" s="73">
         <f>B32/B8*100</f>
         <v>1.7109388926482498</v>
       </c>
@@ -4378,7 +4325,7 @@
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="105">
+      <c r="B37" s="73">
         <f>E32/B20</f>
         <v>0.80407786557345728</v>
       </c>
@@ -4462,7 +4409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30034036-F45B-4455-9AE2-0E822A6177AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4485,11 +4432,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
       <c r="G1" s="6" t="s">
         <v>60</v>
       </c>
@@ -4517,13 +4464,13 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="77" t="s">
         <v>237</v>
       </c>
       <c r="B2" s="1">
         <v>1.3380000000000001</v>
       </c>
-      <c r="C2" s="130" t="s">
+      <c r="C2" s="82" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -4553,13 +4500,13 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="128" t="s">
+      <c r="A3" s="80" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="1">
         <v>120</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="82" t="s">
         <v>73</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -4589,13 +4536,13 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="128" t="s">
+      <c r="A4" s="80" t="s">
         <v>238</v>
       </c>
       <c r="B4" s="1">
         <v>27</v>
       </c>
-      <c r="C4" s="130" t="s">
+      <c r="C4" s="82" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -4619,13 +4566,13 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="80" t="s">
         <v>239</v>
       </c>
       <c r="B5" s="1">
         <v>15000</v>
       </c>
-      <c r="C5" s="130" t="s">
+      <c r="C5" s="82" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -4649,9 +4596,9 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="126"/>
+      <c r="A6" s="79"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="130"/>
+      <c r="C6" s="82"/>
       <c r="G6" s="1" t="s">
         <v>83</v>
       </c>
@@ -4673,14 +4620,14 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="80" t="s">
         <v>240</v>
       </c>
       <c r="B7" s="1">
         <f>B4/B3</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="C7" s="130" t="s">
+      <c r="C7" s="82" t="s">
         <v>86</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -4704,14 +4651,14 @@
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="77" t="s">
         <v>241</v>
       </c>
       <c r="B8" s="1">
         <f>B4*B5</f>
         <v>405000</v>
       </c>
-      <c r="C8" s="130" t="s">
+      <c r="C8" s="82" t="s">
         <v>80</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -4730,9 +4677,9 @@
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="126"/>
+      <c r="A9" s="79"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="130"/>
+      <c r="C9" s="82"/>
       <c r="O9" s="1" t="s">
         <v>90</v>
       </c>
@@ -4743,185 +4690,185 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="128" t="s">
+      <c r="A10" s="80" t="s">
         <v>91</v>
       </c>
       <c r="B10" s="1">
         <f>B8*M3</f>
         <v>44550</v>
       </c>
-      <c r="C10" s="130" t="s">
+      <c r="C10" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="128"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="128" t="s">
+      <c r="A11" s="80" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="1">
         <v>0.75</v>
       </c>
-      <c r="C11" s="130" t="s">
+      <c r="C11" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13" t="s">
+      <c r="G11" s="125"/>
+      <c r="H11" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="128"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="130"/>
-      <c r="G12" s="14" t="s">
+      <c r="C12" s="82"/>
+      <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="8">
         <v>395</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="8">
         <v>1.6</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="8">
         <v>20</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="8">
         <v>0.7</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="8">
         <v>34</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="124" t="s">
+      <c r="A13" s="77" t="s">
         <v>104</v>
       </c>
       <c r="B13" s="1">
         <f>B10*B11</f>
         <v>33412.5</v>
       </c>
-      <c r="C13" s="130" t="s">
+      <c r="C13" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="8">
         <v>9</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="8">
         <v>6</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="8">
         <v>33</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="8">
         <v>20</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="8">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="80" t="s">
         <v>242</v>
       </c>
       <c r="B14" s="1">
         <f>B13</f>
         <v>33412.5</v>
       </c>
-      <c r="C14" s="130" t="s">
+      <c r="C14" s="82" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="128" t="s">
+      <c r="A16" s="80" t="s">
         <v>110</v>
       </c>
       <c r="B16" s="1">
         <f>B14*B2</f>
         <v>44705.925000000003</v>
       </c>
-      <c r="C16" s="130" t="s">
+      <c r="C16" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="126" t="s">
+      <c r="D16" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="126" t="s">
+      <c r="E16" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="8">
         <f>B4</f>
         <v>27</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="12">
         <f>H16*3</f>
         <v>81</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="12">
         <f>B21*I16*2</f>
         <v>32.4</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="128" t="s">
+      <c r="A17" s="80" t="s">
         <v>110</v>
       </c>
       <c r="B17" s="1">
         <f>B16/1000</f>
         <v>44.705925000000001</v>
       </c>
-      <c r="C17" s="130" t="s">
+      <c r="C17" s="82" t="s">
         <v>113</v>
       </c>
       <c r="D17" s="1">
@@ -4931,335 +4878,335 @@
         <f>B17/5</f>
         <v>8.9411850000000008</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="124" t="s">
+      <c r="A19" s="77" t="s">
         <v>241</v>
       </c>
       <c r="B19" s="1">
         <f>B20*B21</f>
         <v>5.4</v>
       </c>
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="79" t="s">
         <v>115</v>
       </c>
       <c r="B20" s="1">
         <f>B4</f>
         <v>27</v>
       </c>
-      <c r="C20" s="130"/>
-      <c r="G20" s="14" t="s">
+      <c r="C20" s="82"/>
+      <c r="G20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="79" t="s">
         <v>116</v>
       </c>
       <c r="B21" s="1">
         <f>0.2</f>
         <v>0.2</v>
       </c>
-      <c r="C21" s="130" t="s">
+      <c r="C21" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="129" t="s">
+      <c r="A23" s="81" t="s">
         <v>117</v>
       </c>
       <c r="B23" s="1">
         <f>H34</f>
         <v>0</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="129" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="21"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="130"/>
+      <c r="N23" s="130"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="131"/>
     </row>
     <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J24" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="L24" s="23" t="s">
+      <c r="L24" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="M24" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="N24" s="24" t="s">
+      <c r="N24" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="O24" s="25" t="s">
+      <c r="O24" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="P24" s="22" t="s">
+      <c r="P24" s="14" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="128" t="s">
+      <c r="A25" s="80" t="s">
         <v>243</v>
       </c>
       <c r="B25" s="1">
         <f>B26*B27*B28</f>
         <v>3.4999999999999999E-6</v>
       </c>
-      <c r="C25" s="130" t="s">
+      <c r="C25" s="82" t="s">
         <v>129</v>
       </c>
       <c r="D25" s="1">
         <f>D26*D27*D28</f>
         <v>3500</v>
       </c>
-      <c r="E25" s="130" t="s">
+      <c r="E25" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="15">
         <v>19.8</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K25" s="23">
+      <c r="K25" s="15">
         <v>0</v>
       </c>
-      <c r="L25" s="23">
+      <c r="L25" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="16">
         <v>0</v>
       </c>
-      <c r="O25" s="25">
+      <c r="O25" s="17">
         <f>0.18*10^-6</f>
         <v>1.8E-7</v>
       </c>
-      <c r="P25" s="22">
+      <c r="P25" s="14">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="126" t="s">
+      <c r="A26" s="79" t="s">
         <v>116</v>
       </c>
       <c r="B26" s="1">
         <f>B21</f>
         <v>0.2</v>
       </c>
-      <c r="C26" s="130"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="1">
         <f>B26*1000</f>
         <v>200</v>
       </c>
-      <c r="E26" s="130" t="s">
+      <c r="E26" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="99">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="99">
         <v>6.9</v>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="99">
         <v>0.8</v>
       </c>
-      <c r="K26" s="27">
+      <c r="K26" s="99">
         <v>0</v>
       </c>
-      <c r="L26" s="27">
+      <c r="L26" s="99">
         <v>0.19</v>
       </c>
-      <c r="M26" s="27">
+      <c r="M26" s="99">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="27">
+      <c r="N26" s="99">
         <v>0.85</v>
       </c>
-      <c r="O26" s="27" t="s">
+      <c r="O26" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="P26" s="27">
+      <c r="P26" s="99">
         <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="126" t="s">
+      <c r="A27" s="79" t="s">
         <v>134</v>
       </c>
       <c r="B27" s="1">
         <f>10/1000</f>
         <v>0.01</v>
       </c>
-      <c r="C27" s="130" t="s">
+      <c r="C27" s="82" t="s">
         <v>114</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" ref="D27" si="0">B27*1000</f>
         <v>10</v>
       </c>
-      <c r="E27" s="130" t="s">
+      <c r="E27" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
     </row>
     <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
+      <c r="A28" s="79" t="s">
         <v>136</v>
       </c>
       <c r="B28" s="1">
         <f>1.75/1000</f>
         <v>1.75E-3</v>
       </c>
-      <c r="C28" s="130" t="s">
+      <c r="C28" s="82" t="s">
         <v>114</v>
       </c>
       <c r="D28" s="1">
         <f>B28*1000</f>
         <v>1.75</v>
       </c>
-      <c r="E28" s="130" t="s">
+      <c r="E28" s="82" t="s">
         <v>131</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="15">
         <v>28.5</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="15">
         <v>3.5</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="15">
         <v>0.6</v>
       </c>
-      <c r="K28" s="23">
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="23">
+      <c r="L28" s="15">
         <v>0.11</v>
       </c>
-      <c r="M28" s="23">
+      <c r="M28" s="15">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="N28" s="24">
+      <c r="N28" s="16">
         <v>0.88</v>
       </c>
-      <c r="O28" s="25" t="s">
+      <c r="O28" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="P28" s="22">
+      <c r="P28" s="14">
         <v>0.83199999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="15">
         <v>6.2</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="15">
         <v>3.5</v>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="15">
         <v>0.3</v>
       </c>
-      <c r="L29" s="23">
+      <c r="L29" s="15">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="15">
         <v>0</v>
       </c>
-      <c r="N29" s="24">
+      <c r="N29" s="16">
         <v>0</v>
       </c>
-      <c r="O29" s="25" t="s">
+      <c r="O29" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="P29" s="22">
+      <c r="P29" s="14">
         <v>4.72</v>
       </c>
     </row>
@@ -5269,35 +5216,35 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="122" t="s">
         <v>142</v>
       </c>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29" t="s">
+      <c r="G31" s="122"/>
+      <c r="H31" s="122" t="s">
         <v>143</v>
       </c>
-      <c r="I31" s="29" t="s">
+      <c r="I31" s="122" t="s">
         <v>144</v>
       </c>
-      <c r="J31" s="30" t="s">
+      <c r="J31" s="123" t="s">
         <v>145</v>
       </c>
-      <c r="K31" s="30"/>
+      <c r="K31" s="123"/>
     </row>
     <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="128" t="s">
+      <c r="A32" s="80" t="s">
         <v>247</v>
       </c>
       <c r="B32" s="1">
         <v>16.7</v>
       </c>
-      <c r="C32" s="130" t="s">
+      <c r="C32" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="122"/>
       <c r="J32" s="1" t="s">
         <v>147</v>
       </c>
@@ -5306,20 +5253,20 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="128" t="s">
+      <c r="A33" s="80" t="s">
         <v>248</v>
       </c>
       <c r="B33" s="1">
         <f>B17/B32</f>
         <v>2.6770014970059881</v>
       </c>
-      <c r="C33" s="130" t="s">
+      <c r="C33" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H33" s="1">
@@ -5330,50 +5277,50 @@
         <f>B19*H25*24*365</f>
         <v>936619.20000000019</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="115">
         <f>SUM(H33:I33)</f>
         <v>14134556.699999999</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="115">
         <f>J33/365</f>
         <v>38724.812876712327</v>
       </c>
-      <c r="N33" s="33"/>
+      <c r="N33" s="20"/>
     </row>
     <row r="34" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="128" t="s">
+      <c r="A34" s="80" t="s">
         <v>249</v>
       </c>
       <c r="B34" s="1">
         <f>[1]Лист1!B46/10000</f>
         <v>3.8970873005464479E-2</v>
       </c>
-      <c r="C34" s="130" t="s">
+      <c r="C34" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="32" t="s">
+      <c r="F34" s="115"/>
+      <c r="G34" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
+      <c r="J34" s="115"/>
+      <c r="K34" s="115"/>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="128" t="s">
+      <c r="A35" s="80" t="s">
         <v>250</v>
       </c>
-      <c r="B35" s="131">
+      <c r="B35" s="83">
         <f>B34+B33</f>
         <v>2.7159723700114524</v>
       </c>
-      <c r="C35" s="130" t="s">
+      <c r="C35" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F35" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H35" s="1">
@@ -5384,41 +5331,41 @@
         <f>B19*L25*24*365</f>
         <v>3311.28</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="115">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>56771.28</v>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="115">
         <f>J35/365</f>
         <v>155.53775342465752</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32" t="s">
+      <c r="F36" s="115"/>
+      <c r="G36" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
+      <c r="J36" s="115"/>
+      <c r="K36" s="115"/>
     </row>
     <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="124" t="s">
+      <c r="A37" s="77" t="s">
         <v>251</v>
       </c>
       <c r="B37" s="1">
         <f>B35*1.25</f>
         <v>3.3949654625143157</v>
       </c>
-      <c r="C37" s="130" t="s">
+      <c r="C37" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H37" s="1">
@@ -5429,36 +5376,36 @@
         <f>B19*J25*24*365</f>
         <v>13245.12</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="115">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>681495.12</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="115">
         <f>J37/365</f>
         <v>1867.1099178082191</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="31"/>
-      <c r="G38" s="32" t="s">
+      <c r="F38" s="115"/>
+      <c r="G38" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
+      <c r="J38" s="115"/>
+      <c r="K38" s="115"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="128" t="s">
+      <c r="A39" s="80" t="s">
         <v>154</v>
       </c>
       <c r="B39" s="1">
         <v>12</v>
       </c>
-      <c r="F39" s="31" t="s">
+      <c r="F39" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="G39" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H39" s="1">
@@ -5469,43 +5416,43 @@
         <f>B19*M25*24*365</f>
         <v>1655.64</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="115">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>25044.39</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="115">
         <f>J39/365</f>
         <v>68.614767123287663</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="128" t="s">
+      <c r="A40" s="80" t="s">
         <v>155</v>
       </c>
       <c r="B40" s="1">
         <v>16</v>
       </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="32" t="s">
+      <c r="F40" s="115"/>
+      <c r="G40" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
+      <c r="J40" s="115"/>
+      <c r="K40" s="115"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="124" t="s">
+      <c r="A41" s="77" t="s">
         <v>156</v>
       </c>
       <c r="B41" s="1">
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="G41" s="32" t="s">
+      <c r="G41" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H41" s="1">
@@ -5516,37 +5463,37 @@
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="115">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="115">
         <f>J41/365</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="124" t="s">
+      <c r="A42" s="77" t="s">
         <v>252</v>
       </c>
       <c r="B42" s="1">
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="32" t="s">
+      <c r="F42" s="115"/>
+      <c r="G42" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
+      <c r="J42" s="115"/>
+      <c r="K42" s="115"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="31" t="s">
+      <c r="F43" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="G43" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H43" s="1">
@@ -5557,48 +5504,48 @@
         <f>B19*I25*24*365</f>
         <v>108799.2</v>
       </c>
-      <c r="J43" s="31">
+      <c r="J43" s="115">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>1244824.2</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="115">
         <f>J43/365</f>
         <v>3410.4772602739727</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="124" t="s">
+      <c r="A44" s="77" t="s">
         <v>159</v>
       </c>
       <c r="B44" s="1">
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="C44" s="130"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="32" t="s">
+      <c r="C44" s="82"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
+      <c r="J44" s="115"/>
+      <c r="K44" s="115"/>
     </row>
     <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="124" t="s">
+      <c r="A45" s="77" t="s">
         <v>160</v>
       </c>
       <c r="B45" s="1">
         <f>J33/1000</f>
         <v>14134.556699999999</v>
       </c>
-      <c r="C45" s="130" t="s">
+      <c r="C45" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="F45" s="31" t="s">
+      <c r="F45" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="32" t="s">
+      <c r="G45" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H45" s="1">
@@ -5606,50 +5553,50 @@
         <v>66825</v>
       </c>
       <c r="I45" s="1"/>
-      <c r="J45" s="31">
+      <c r="J45" s="115">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>66825</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="115">
         <f>J45/365</f>
         <v>183.08219178082192</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="124" t="s">
+      <c r="A46" s="77" t="s">
         <v>162</v>
       </c>
       <c r="B46" s="1">
         <f>(B44*B45)+([1]Лист1!B27*1000)</f>
         <v>41972.847399977145</v>
       </c>
-      <c r="C46" s="130" t="s">
+      <c r="C46" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32" t="s">
+      <c r="F46" s="115"/>
+      <c r="G46" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
+      <c r="J46" s="115"/>
+      <c r="K46" s="115"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="124" t="s">
+      <c r="A47" s="77" t="s">
         <v>162</v>
       </c>
       <c r="B47" s="1">
         <f>B46/1000</f>
         <v>41.972847399977148</v>
       </c>
-      <c r="C47" s="130" t="s">
+      <c r="C47" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="F47" s="31" t="s">
+      <c r="F47" s="115" t="s">
         <v>163</v>
       </c>
-      <c r="G47" s="32" t="s">
+      <c r="G47" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H47" s="1"/>
@@ -5657,30 +5604,30 @@
         <f>B19*P25*24*365</f>
         <v>2034.0719999999999</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="115">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>2034.0719999999999</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="115">
         <f>J47/365</f>
         <v>5.5728</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="31"/>
-      <c r="G48" s="32" t="s">
+      <c r="F48" s="115"/>
+      <c r="G48" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
+      <c r="J48" s="115"/>
+      <c r="K48" s="115"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="31" t="s">
+      <c r="F49" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="G49" s="32" t="s">
+      <c r="G49" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H49" s="1"/>
@@ -5688,642 +5635,679 @@
         <f>B19*O25*24*365</f>
         <v>8.5147199999999999E-3</v>
       </c>
-      <c r="J49" s="31">
+      <c r="J49" s="115">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>8.5147199999999999E-3</v>
       </c>
-      <c r="K49" s="31">
+      <c r="K49" s="115">
         <f>J49/365</f>
         <v>2.3328000000000001E-5</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="31"/>
-      <c r="G50" s="32" t="s">
+      <c r="F50" s="115"/>
+      <c r="G50" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
+      <c r="J50" s="115"/>
+      <c r="K50" s="115"/>
     </row>
     <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="124" t="s">
+      <c r="A51" s="77" t="s">
         <v>253</v>
       </c>
       <c r="B51" s="1">
         <f>(B47/[1]Лист1!Q1)/10000</f>
         <v>2.5438089333319485</v>
       </c>
-      <c r="C51" s="130" t="s">
+      <c r="C51" s="82" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="124" t="s">
+      <c r="A52" s="77" t="s">
         <v>254</v>
       </c>
       <c r="B52" s="1">
         <f>B51*1.25</f>
         <v>3.1797611666649357</v>
       </c>
-      <c r="C52" s="130" t="s">
+      <c r="C52" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="G52" s="34" t="s">
+      <c r="G52" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="H52" s="35" t="s">
+      <c r="H52" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="I52" s="36" t="s">
+      <c r="I52" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="J52" s="37"/>
+      <c r="J52" s="24"/>
     </row>
     <row r="53" spans="1:11" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I53" s="38" t="s">
+      <c r="I53" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="J53" s="39" t="s">
+      <c r="J53" s="26" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="124" t="s">
+      <c r="A54" s="77" t="s">
         <v>172</v>
       </c>
       <c r="B54" s="1">
         <f>SUM(I16:I21)</f>
         <v>81</v>
       </c>
-      <c r="C54" s="130" t="s">
+      <c r="C54" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="G54" s="40" t="s">
+      <c r="G54" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="H54" s="41">
-        <f>K33*1000/$D$25</f>
-        <v>11064.232250489236</v>
-      </c>
-      <c r="I54" s="42">
+      <c r="H54" s="28">
+        <f>K33/$D$25</f>
+        <v>11.064232250489237</v>
+      </c>
+      <c r="I54" s="29">
         <f>K33/J71</f>
         <v>12908.27095890411</v>
       </c>
-      <c r="J54" s="43">
+      <c r="J54" s="30">
         <f>H54/J71</f>
-        <v>3688.0774168297453</v>
+        <v>3.6880774168297457</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G55" s="34" t="s">
+      <c r="G55" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="H55" s="44">
-        <f>K35*1000/$D$25</f>
-        <v>44.439358121330727</v>
-      </c>
-      <c r="I55" s="45">
+      <c r="H55" s="31">
+        <f>K35/$D$25</f>
+        <v>4.4439358121330721E-2</v>
+      </c>
+      <c r="I55" s="32">
         <f>K35/J78</f>
         <v>3110.7550684931502</v>
       </c>
-      <c r="J55" s="46">
+      <c r="J55" s="33">
         <f>H55/J78</f>
-        <v>888.78716242661449</v>
+        <v>0.88878716242661437</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G56" s="34" t="s">
+      <c r="A56" s="133"/>
+      <c r="B56" s="133"/>
+      <c r="C56" s="133"/>
+      <c r="G56" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H56" s="44">
-        <f>K37*1000/$D$25</f>
-        <v>533.45997651663401</v>
-      </c>
-      <c r="I56" s="45">
+      <c r="H56" s="31">
+        <f>K37/$D$25</f>
+        <v>0.53345997651663402</v>
+      </c>
+      <c r="I56" s="32">
         <f>K37/J68</f>
         <v>46677.747945205476</v>
       </c>
-      <c r="J56" s="46">
+      <c r="J56" s="33">
         <f>H56/J68</f>
-        <v>13336.499412915849</v>
+        <v>13.336499412915851</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G57" s="34" t="s">
+      <c r="A57" s="134"/>
+      <c r="B57" s="134"/>
+      <c r="C57" s="134"/>
+      <c r="G57" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="H57" s="44">
-        <f>K39*1000/$D$25</f>
-        <v>19.60421917808219</v>
-      </c>
-      <c r="I57" s="45">
+      <c r="H57" s="31">
+        <f>K39/$D$25</f>
+        <v>1.960421917808219E-2</v>
+      </c>
+      <c r="I57" s="32">
         <f>K39/J70</f>
         <v>228715.89041095891</v>
       </c>
-      <c r="J57" s="46">
+      <c r="J57" s="33">
         <f>H57/J70</f>
-        <v>65347.397260273974</v>
+        <v>65.347397260273979</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G58" s="34" t="s">
+      <c r="A58" s="134"/>
+      <c r="B58" s="134"/>
+      <c r="C58" s="134"/>
+      <c r="G58" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="H58" s="44">
-        <f>K41*1000/$D$25</f>
+      <c r="H58" s="31">
+        <f>K41/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I58" s="45">
+      <c r="I58" s="32">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-      <c r="J58" s="46">
+      <c r="J58" s="33">
         <f>H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G59" s="34" t="s">
+      <c r="A59" s="134"/>
+      <c r="B59" s="134"/>
+      <c r="C59" s="134"/>
+      <c r="G59" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H59" s="44">
-        <f>K43*1000/$D$25</f>
-        <v>974.42207436399212</v>
-      </c>
-      <c r="I59" s="45">
+      <c r="H59" s="31">
+        <f>K43/$D$25</f>
+        <v>0.9744220743639922</v>
+      </c>
+      <c r="I59" s="32">
         <f>K43/J74</f>
         <v>682095.45205479453</v>
       </c>
-      <c r="J59" s="46">
+      <c r="J59" s="33">
         <f>H59/J74</f>
-        <v>194884.41487279843</v>
+        <v>194.88441487279843</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G60" s="34" t="s">
+      <c r="G60" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="H60" s="44">
-        <f>K45*1000/$D$25</f>
-        <v>52.309197651663403</v>
-      </c>
-      <c r="I60" s="45">
+      <c r="H60" s="31">
+        <f>K45/$D$25</f>
+        <v>5.2309197651663406E-2</v>
+      </c>
+      <c r="I60" s="32">
         <f>K45/J69</f>
         <v>3661.6438356164381</v>
       </c>
-      <c r="J60" s="46">
+      <c r="J60" s="33">
         <f>H60/J69</f>
-        <v>1046.1839530332679</v>
+        <v>1.0461839530332679</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G61" s="34" t="s">
+      <c r="G61" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="H61" s="44">
-        <f>K47*1000/$D$25</f>
-        <v>1.5922285714285715</v>
-      </c>
-      <c r="I61" s="45">
+      <c r="H61" s="31">
+        <f>K47/$D$25</f>
+        <v>1.5922285714285713E-3</v>
+      </c>
+      <c r="I61" s="32">
         <f>K47/J85</f>
         <v>92.88000000000001</v>
       </c>
-      <c r="J61" s="46">
+      <c r="J61" s="33">
         <f>H61/J85</f>
-        <v>26.537142857142861</v>
+        <v>2.6537142857142856E-2</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="15" t="s">
+      <c r="G62" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="H62" s="47">
-        <f>K49*1000/$D$25</f>
-        <v>6.6651428571428579E-6</v>
-      </c>
-      <c r="I62" s="48">
+      <c r="H62" s="34">
+        <f>K49/$D$25</f>
+        <v>6.6651428571428573E-9</v>
+      </c>
+      <c r="I62" s="35">
         <f>K49/J81</f>
         <v>23.328000000000003</v>
       </c>
-      <c r="J62" s="49">
+      <c r="J62" s="36">
         <f>H62/J81</f>
-        <v>6.6651428571428584</v>
+        <v>6.6651428571428573E-3</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="50" t="s">
+      <c r="G64" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="H64" s="35" t="s">
+      <c r="H64" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="I64" s="51" t="s">
+      <c r="I64" s="116" t="s">
         <v>178</v>
       </c>
-      <c r="J64" s="52"/>
+      <c r="J64" s="117"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="53"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="56"/>
+      <c r="G65" s="103"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="118"/>
+      <c r="J65" s="119"/>
     </row>
     <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="53"/>
-      <c r="H66" s="57" t="s">
+      <c r="G66" s="103"/>
+      <c r="H66" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="I66" s="58" t="s">
+      <c r="I66" s="120" t="s">
         <v>180</v>
       </c>
-      <c r="J66" s="59"/>
+      <c r="J66" s="121"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="60"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="13" t="s">
+      <c r="G67" s="104"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="J67" s="8" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="14" t="s">
+      <c r="G68" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H68" s="8">
         <v>2</v>
       </c>
-      <c r="I68" s="13">
+      <c r="I68" s="8">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J68" s="13">
+      <c r="J68" s="8">
         <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="124" t="s">
+      <c r="A69" s="77" t="s">
         <v>184</v>
       </c>
       <c r="B69" s="1">
         <v>0.4</v>
       </c>
-      <c r="G69" s="14" t="s">
+      <c r="G69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="8">
         <v>3</v>
       </c>
-      <c r="I69" s="13">
+      <c r="I69" s="8">
         <v>0.15</v>
       </c>
-      <c r="J69" s="13">
+      <c r="J69" s="8">
         <v>0.05</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="124" t="s">
+      <c r="A70" s="77" t="s">
         <v>185</v>
       </c>
       <c r="B70" s="1">
         <v>1</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="8">
         <v>1</v>
       </c>
-      <c r="I70" s="13">
+      <c r="I70" s="8">
         <v>1E-3</v>
       </c>
-      <c r="J70" s="13">
+      <c r="J70" s="8">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="124" t="s">
+      <c r="A71" s="77" t="s">
         <v>244</v>
       </c>
       <c r="B71" s="1">
         <v>1.5</v>
       </c>
-      <c r="G71" s="40" t="s">
+      <c r="G71" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="H71" s="50">
+      <c r="H71" s="102">
         <v>3</v>
       </c>
-      <c r="I71" s="50">
+      <c r="I71" s="102">
         <v>5</v>
       </c>
-      <c r="J71" s="50">
+      <c r="J71" s="102">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A72" s="124" t="s">
+      <c r="A72" s="77" t="s">
         <v>188</v>
       </c>
       <c r="B72" s="1">
         <v>1</v>
       </c>
-      <c r="G72" s="62"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="103"/>
+      <c r="I72" s="103"/>
+      <c r="J72" s="103"/>
     </row>
     <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="124" t="s">
+      <c r="A73" s="77" t="s">
         <v>189</v>
       </c>
       <c r="B73" s="1">
         <v>1</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H73" s="60"/>
-      <c r="I73" s="60"/>
-      <c r="J73" s="60"/>
+      <c r="H73" s="104"/>
+      <c r="I73" s="104"/>
+      <c r="J73" s="104"/>
     </row>
     <row r="74" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A74" s="124" t="s">
+      <c r="A74" s="77" t="s">
         <v>192</v>
       </c>
       <c r="B74" s="1">
         <f>SUM(J99:J102)</f>
         <v>5</v>
       </c>
-      <c r="G74" s="40" t="s">
+      <c r="G74" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="H74" s="50">
+      <c r="H74" s="102">
         <v>4</v>
       </c>
-      <c r="I74" s="50">
+      <c r="I74" s="102">
         <v>0.03</v>
       </c>
-      <c r="J74" s="50">
+      <c r="J74" s="102">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G75" s="62"/>
-      <c r="H75" s="53"/>
-      <c r="I75" s="53"/>
-      <c r="J75" s="53"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="103"/>
+      <c r="I75" s="103"/>
+      <c r="J75" s="103"/>
     </row>
     <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="H76" s="60"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="60"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
+      <c r="J76" s="104"/>
     </row>
     <row r="77" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="124" t="s">
+      <c r="A77" s="77" t="s">
         <v>246</v>
       </c>
       <c r="B77" s="1">
         <f>(0.5+0.01*B54*B74)*B69*B70*B71*B72*B73</f>
         <v>2.7300000000000004</v>
       </c>
-      <c r="C77" s="130" t="s">
+      <c r="C77" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H77" s="13">
+      <c r="H77" s="8">
         <v>3</v>
       </c>
-      <c r="I77" s="13">
+      <c r="I77" s="8">
         <v>0.5</v>
       </c>
-      <c r="J77" s="13">
+      <c r="J77" s="8">
         <v>0.15</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G78" s="40" t="s">
+      <c r="G78" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="H78" s="50">
+      <c r="H78" s="102">
         <v>2</v>
       </c>
-      <c r="I78" s="50">
+      <c r="I78" s="102">
         <v>0.5</v>
       </c>
-      <c r="J78" s="50">
+      <c r="J78" s="102">
         <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="62"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="103"/>
+      <c r="I79" s="103"/>
+      <c r="J79" s="103"/>
     </row>
     <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="H80" s="60"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="60"/>
-    </row>
-    <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G81" s="40" t="s">
+      <c r="H80" s="104"/>
+      <c r="I80" s="104"/>
+      <c r="J80" s="104"/>
+    </row>
+    <row r="81" spans="7:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G81" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="H81" s="50">
+      <c r="H81" s="102">
         <v>1</v>
       </c>
-      <c r="I81" s="63"/>
-      <c r="J81" s="64">
+      <c r="I81" s="109"/>
+      <c r="J81" s="112">
         <f>10^-6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="82" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G82" s="62"/>
-      <c r="H82" s="53"/>
-      <c r="I82" s="65"/>
-      <c r="J82" s="66"/>
-    </row>
-    <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G83" s="14" t="s">
+    <row r="82" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G82" s="40"/>
+      <c r="H82" s="103"/>
+      <c r="I82" s="110"/>
+      <c r="J82" s="113"/>
+    </row>
+    <row r="83" spans="7:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="H83" s="60"/>
-      <c r="I83" s="67"/>
-      <c r="J83" s="68"/>
-    </row>
-    <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G84" s="14" t="s">
+      <c r="H83" s="104"/>
+      <c r="I83" s="111"/>
+      <c r="J83" s="114"/>
+    </row>
+    <row r="84" spans="7:14" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H84" s="13">
+      <c r="H84" s="8">
         <v>3</v>
       </c>
-      <c r="I84" s="13">
+      <c r="I84" s="8">
         <v>0.5</v>
       </c>
-      <c r="J84" s="13">
+      <c r="J84" s="8">
         <v>0.15</v>
       </c>
     </row>
-    <row r="85" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G85" s="14" t="s">
+    <row r="85" spans="7:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H85" s="13">
+      <c r="H85" s="8">
         <v>2</v>
       </c>
-      <c r="I85" s="13">
+      <c r="I85" s="8">
         <v>0.4</v>
       </c>
-      <c r="J85" s="13">
+      <c r="J85" s="8">
         <v>0.06</v>
       </c>
     </row>
-    <row r="86" spans="7:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="7:10" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="69" t="s">
+    <row r="86" spans="7:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="7:14" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="H87" s="70" t="s">
+      <c r="H87" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="I87" s="70" t="s">
+      <c r="I87" s="42" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="88" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G88" s="71" t="s">
+      <c r="L87" s="144" t="s">
+        <v>234</v>
+      </c>
+      <c r="M87" s="145"/>
+      <c r="N87" s="146"/>
+    </row>
+    <row r="88" spans="7:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G88" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="H88" s="72">
+      <c r="H88" s="44">
         <f>K33*1000/$D$25</f>
         <v>11064.232250489236</v>
       </c>
-      <c r="I88" s="72">
+      <c r="I88" s="44">
         <f>K33/J71</f>
         <v>12908.27095890411</v>
       </c>
-    </row>
-    <row r="89" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G89" s="73" t="s">
+      <c r="L88" s="141" t="s">
+        <v>255</v>
+      </c>
+      <c r="M88" s="142"/>
+      <c r="N88" s="143"/>
+    </row>
+    <row r="89" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G89" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="H89" s="74">
+      <c r="H89" s="46">
         <f>K35*1000/$D$25</f>
         <v>44.439358121330727</v>
       </c>
-      <c r="I89" s="74">
+      <c r="I89" s="46">
         <f>K35/J78</f>
         <v>3110.7550684931502</v>
       </c>
-    </row>
-    <row r="90" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G90" s="73" t="s">
+      <c r="L89" s="135"/>
+      <c r="M89" s="136"/>
+      <c r="N89" s="137"/>
+    </row>
+    <row r="90" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G90" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="H90" s="74">
+      <c r="H90" s="46">
         <f>K37*1000/$D$25</f>
         <v>533.45997651663401</v>
       </c>
-      <c r="I90" s="74">
+      <c r="I90" s="46">
         <f>K37/J68</f>
         <v>46677.747945205476</v>
       </c>
-    </row>
-    <row r="91" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G91" s="73" t="s">
+      <c r="L90" s="135"/>
+      <c r="M90" s="136"/>
+      <c r="N90" s="137"/>
+    </row>
+    <row r="91" spans="7:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G91" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="H91" s="74">
+      <c r="H91" s="46">
         <f>K39*1000/$D$25</f>
         <v>19.60421917808219</v>
       </c>
-      <c r="I91" s="74">
+      <c r="I91" s="46">
         <f>K39/J70</f>
         <v>228715.89041095891</v>
       </c>
-    </row>
-    <row r="92" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G92" s="73" t="s">
+      <c r="L91" s="135"/>
+      <c r="M91" s="136"/>
+      <c r="N91" s="137"/>
+    </row>
+    <row r="92" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G92" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="H92" s="74">
+      <c r="H92" s="46">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I92" s="74">
+      <c r="I92" s="46">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="7:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="G93" s="74" t="s">
+      <c r="L92" s="135"/>
+      <c r="M92" s="136"/>
+      <c r="N92" s="137"/>
+    </row>
+    <row r="93" spans="7:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G93" s="46" t="s">
         <v>203</v>
       </c>
-      <c r="H93" s="74">
+      <c r="H93" s="46">
         <f>K43*1000/$D$25</f>
         <v>974.42207436399212</v>
       </c>
-      <c r="I93" s="74">
+      <c r="I93" s="46">
         <f>K43/J74</f>
         <v>682095.45205479453</v>
       </c>
-    </row>
-    <row r="94" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G94" s="73" t="s">
+      <c r="L93" s="138"/>
+      <c r="M93" s="139"/>
+      <c r="N93" s="140"/>
+    </row>
+    <row r="94" spans="7:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G94" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="H94" s="74">
+      <c r="H94" s="46">
         <f>K45*1000/$D$25</f>
         <v>52.309197651663403</v>
       </c>
-      <c r="I94" s="74">
+      <c r="I94" s="46">
         <f>K45/J69</f>
         <v>3661.6438356164381</v>
       </c>
     </row>
-    <row r="95" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G95" s="73" t="s">
+    <row r="95" spans="7:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G95" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="H95" s="74">
+      <c r="H95" s="46">
         <f>K47*1000/$D$25</f>
         <v>1.5922285714285715</v>
       </c>
-      <c r="I95" s="74">
+      <c r="I95" s="46">
         <f>K47/J85</f>
         <v>92.88000000000001</v>
       </c>
     </row>
-    <row r="96" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G96" s="75" t="s">
+    <row r="96" spans="7:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G96" s="47" t="s">
         <v>204</v>
       </c>
-      <c r="H96" s="76">
+      <c r="H96" s="48">
         <f>K49*1000/$D$25</f>
         <v>6.6651428571428579E-6</v>
       </c>
-      <c r="I96" s="76">
+      <c r="I96" s="48">
         <f>K49/J81</f>
         <v>23.328000000000003</v>
       </c>
@@ -6332,17 +6316,17 @@
       <c r="G98" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="H98" s="77" t="s">
+      <c r="H98" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="I98" s="77" t="s">
+      <c r="I98" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="J98" s="77" t="s">
+      <c r="J98" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="K98" s="122"/>
-      <c r="L98" s="123"/>
+      <c r="K98" s="75"/>
+      <c r="L98" s="76"/>
     </row>
     <row r="99" spans="7:12" x14ac:dyDescent="0.25">
       <c r="G99" s="1" t="s">
@@ -6409,214 +6393,272 @@
     </row>
     <row r="103" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="7:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G104" s="78" t="s">
+      <c r="G104" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="H104" s="27" t="s">
+      <c r="H104" s="99" t="s">
         <v>213</v>
       </c>
-      <c r="I104" s="35" t="s">
+      <c r="I104" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="J104" s="50" t="s">
+      <c r="J104" s="102" t="s">
         <v>214</v>
       </c>
-      <c r="K104" s="79" t="s">
+      <c r="K104" s="105" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="105" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="G105" s="80"/>
-      <c r="H105" s="81"/>
-      <c r="I105" s="54"/>
-      <c r="J105" s="53"/>
-      <c r="K105" s="82"/>
+      <c r="G105" s="51"/>
+      <c r="H105" s="100"/>
+      <c r="I105" s="37"/>
+      <c r="J105" s="103"/>
+      <c r="K105" s="106"/>
     </row>
     <row r="106" spans="7:12" ht="54" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G106" s="83" t="s">
+      <c r="G106" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="H106" s="28"/>
-      <c r="I106" s="13" t="s">
+      <c r="H106" s="101"/>
+      <c r="I106" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="J106" s="60"/>
-      <c r="K106" s="84"/>
+      <c r="J106" s="104"/>
+      <c r="K106" s="107"/>
     </row>
     <row r="107" spans="7:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G107" s="78" t="s">
+      <c r="G107" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="H107" s="34">
+      <c r="H107" s="21">
         <f>H25</f>
         <v>19.8</v>
       </c>
-      <c r="I107" s="44">
-        <v>2048.9318982387476</v>
-      </c>
-      <c r="J107" s="35">
+      <c r="I107" s="31">
+        <f>H88</f>
+        <v>11064.232250489236</v>
+      </c>
+      <c r="J107" s="22">
         <f>(H107*$B$77)/$J$54</f>
-        <v>1.4656416851049885E-2</v>
-      </c>
-      <c r="K107" s="85">
+        <v>14.656416851049883</v>
+      </c>
+      <c r="K107" s="53">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G108" s="78" t="s">
+      <c r="G108" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="H108" s="34">
+      <c r="H108" s="21">
         <f>L25</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I108" s="44">
-        <v>8.2295107632093938</v>
-      </c>
-      <c r="J108" s="35">
-        <f t="shared" ref="J108:J115" si="10">(H108*$B$77)/$J$54</f>
-        <v>5.1815615129974346E-5</v>
-      </c>
-      <c r="K108" s="85">
+      <c r="I108" s="31">
+        <f t="shared" ref="I108:I115" si="10">H89</f>
+        <v>44.439358121330727</v>
+      </c>
+      <c r="J108" s="22">
+        <f t="shared" ref="J108:J115" si="11">(H108*$B$77)/$J$54</f>
+        <v>5.1815615129974339E-2</v>
+      </c>
+      <c r="K108" s="53">
         <v>0.05</v>
       </c>
     </row>
     <row r="109" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G109" s="78" t="s">
+      <c r="G109" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H109" s="34">
+      <c r="H109" s="21">
         <f>J25</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="I109" s="44">
-        <v>98.788884540117408</v>
-      </c>
-      <c r="J109" s="35">
+      <c r="I109" s="31">
         <f t="shared" si="10"/>
-        <v>2.0726246051989739E-4</v>
-      </c>
-      <c r="K109" s="85">
+        <v>533.45997651663401</v>
+      </c>
+      <c r="J109" s="22">
+        <f t="shared" si="11"/>
+        <v>0.20726246051989736</v>
+      </c>
+      <c r="K109" s="53">
         <v>0.04</v>
       </c>
     </row>
     <row r="110" spans="7:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G110" s="78" t="s">
+      <c r="G110" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="H110" s="34">
+      <c r="H110" s="21">
         <f>M25</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I110" s="44">
-        <v>3.6304109589041103</v>
-      </c>
-      <c r="J110" s="35">
+      <c r="I110" s="31">
         <f t="shared" si="10"/>
-        <v>2.5907807564987173E-5</v>
-      </c>
-      <c r="K110" s="85">
+        <v>19.60421917808219</v>
+      </c>
+      <c r="J110" s="22">
+        <f t="shared" si="11"/>
+        <v>2.590780756498717E-2</v>
+      </c>
+      <c r="K110" s="53">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="111" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G111" s="78" t="s">
+      <c r="G111" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="H111" s="34">
+      <c r="H111" s="21">
         <f>N25</f>
         <v>0</v>
       </c>
-      <c r="I111" s="44">
-        <v>0</v>
-      </c>
-      <c r="J111" s="35">
+      <c r="I111" s="31">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K111" s="85">
+      <c r="J111" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="53">
         <v>0.15</v>
       </c>
     </row>
     <row r="112" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G112" s="78" t="s">
+      <c r="G112" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="H112" s="34">
+      <c r="H112" s="21">
         <f>I25</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="I112" s="44">
-        <v>180.44853228962816</v>
-      </c>
-      <c r="J112" s="35">
+      <c r="I112" s="31">
         <f t="shared" si="10"/>
-        <v>1.7025130685562996E-3</v>
-      </c>
-      <c r="K112" s="85">
+        <v>974.42207436399212</v>
+      </c>
+      <c r="J112" s="22">
+        <f t="shared" si="11"/>
+        <v>1.7025130685562995</v>
+      </c>
+      <c r="K112" s="53">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="113" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G113" s="78" t="s">
+      <c r="G113" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="H113" s="34">
+      <c r="H113" s="21">
         <f>K25</f>
         <v>0</v>
       </c>
-      <c r="I113" s="44">
-        <v>9.6868884540117435</v>
-      </c>
-      <c r="J113" s="35">
+      <c r="I113" s="31">
         <f t="shared" si="10"/>
+        <v>52.309197651663403</v>
+      </c>
+      <c r="J113" s="22">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K113" s="85">
+      <c r="K113" s="53">
         <v>0.05</v>
       </c>
     </row>
     <row r="114" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G114" s="78" t="s">
+      <c r="G114" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="H114" s="34">
+      <c r="H114" s="21">
         <f>P25</f>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I114" s="44">
-        <v>0.29485714285714287</v>
-      </c>
-      <c r="J114" s="35">
+      <c r="I114" s="31">
         <f t="shared" si="10"/>
-        <v>3.182959215126995E-5</v>
-      </c>
-      <c r="K114" s="85">
+        <v>1.5922285714285715</v>
+      </c>
+      <c r="J114" s="22">
+        <f t="shared" si="11"/>
+        <v>3.1829592151269945E-2</v>
+      </c>
+      <c r="K114" s="53">
         <v>0.06</v>
       </c>
     </row>
     <row r="115" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G115" s="86" t="s">
+      <c r="G115" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="H115" s="15">
+      <c r="H115" s="54">
         <f>O25</f>
         <v>1.8E-7</v>
       </c>
-      <c r="I115" s="48">
-        <v>1.2342857142857142E-6</v>
-      </c>
-      <c r="J115" s="69">
+      <c r="I115" s="132">
         <f t="shared" si="10"/>
-        <v>1.3324015319136257E-10</v>
-      </c>
-      <c r="K115" s="87">
+        <v>6.6651428571428579E-6</v>
+      </c>
+      <c r="J115" s="41">
+        <f t="shared" si="11"/>
+        <v>1.3324015319136258E-7</v>
+      </c>
+      <c r="K115" s="55">
         <f>1/10^6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="65">
+    <mergeCell ref="L87:N87"/>
+    <mergeCell ref="L88:N93"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="H23:P23"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="F31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
     <mergeCell ref="H104:H106"/>
     <mergeCell ref="J104:J106"/>
     <mergeCell ref="K104:K106"/>
@@ -6633,358 +6675,367 @@
     <mergeCell ref="H74:H76"/>
     <mergeCell ref="I74:I76"/>
     <mergeCell ref="J74:J76"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="F31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="H23:P23"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55694E3A-D6B6-4D77-A9F7-241D55EBEBCF}">
-  <dimension ref="A1:K15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="91" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="91" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="91" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="91" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="91" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="91"/>
+    <col min="1" max="1" width="11.7109375" style="59" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="59"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="90" t="s">
+      <c r="C1" s="58" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="H1" s="92"/>
+      <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="94">
-        <f>[2]Лист2!J33</f>
-        <v>2617510.5</v>
-      </c>
-      <c r="C2" s="94">
-        <f>[2]Лист2!J71</f>
+      <c r="B2" s="62">
+        <f>Лист2!J33/1000000</f>
+        <v>14.134556699999999</v>
+      </c>
+      <c r="C2" s="62">
+        <f>Лист2!J71</f>
         <v>3</v>
       </c>
-      <c r="D2" s="94">
+      <c r="D2" s="62">
         <f>1/C2</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E2" s="94">
+      <c r="E2" s="62">
         <v>0.5</v>
       </c>
-      <c r="F2" s="94">
+      <c r="F2" s="62">
         <f>B2*E2*D2</f>
-        <v>436251.75</v>
-      </c>
-      <c r="G2" s="95"/>
+        <v>2.3557594499999999</v>
+      </c>
+      <c r="G2" s="63"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="94">
-        <f>[2]Лист2!J35</f>
-        <v>10513.2</v>
-      </c>
-      <c r="C3" s="94">
-        <f>[2]Лист2!J78</f>
+      <c r="B3" s="62">
+        <f>Лист2!J35/1000000</f>
+        <v>5.677128E-2</v>
+      </c>
+      <c r="C3" s="62">
+        <f>Лист2!J78</f>
         <v>0.05</v>
       </c>
-      <c r="D3" s="94">
+      <c r="D3" s="62">
         <f t="shared" ref="D3:D10" si="0">1/C3</f>
         <v>20</v>
       </c>
-      <c r="E3" s="94">
+      <c r="E3" s="62">
         <v>1</v>
       </c>
-      <c r="F3" s="94">
+      <c r="F3" s="62">
         <f t="shared" ref="F3:F10" si="1">B3*E3*D3</f>
-        <v>210264</v>
+        <v>1.1354256</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="61" t="s">
         <v>225</v>
       </c>
-      <c r="B4" s="94">
-        <f>[2]Лист2!J37</f>
-        <v>126202.8</v>
-      </c>
-      <c r="C4" s="94">
-        <f>[2]Лист2!J68</f>
+      <c r="B4" s="62">
+        <f>Лист2!J37/1000000</f>
+        <v>0.68149512000000001</v>
+      </c>
+      <c r="C4" s="62">
+        <f>Лист2!J68</f>
         <v>0.04</v>
       </c>
-      <c r="D4" s="94">
+      <c r="D4" s="62">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="E4" s="94">
+      <c r="E4" s="62">
         <v>1</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="62">
         <f t="shared" si="1"/>
-        <v>3155070</v>
+        <v>17.037378</v>
       </c>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="94">
-        <f>[2]Лист2!J39</f>
-        <v>4637.8500000000004</v>
-      </c>
-      <c r="C5" s="94">
-        <f>[2]Лист2!J70</f>
+      <c r="B5" s="62">
+        <f>Лист2!J39/1000000</f>
+        <v>2.504439E-2</v>
+      </c>
+      <c r="C5" s="62">
+        <f>Лист2!J70</f>
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="62">
         <f t="shared" si="0"/>
         <v>3333.3333333333335</v>
       </c>
-      <c r="E5" s="94">
+      <c r="E5" s="62">
         <v>4</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="62">
         <f t="shared" si="1"/>
-        <v>61838000.000000007</v>
+        <v>333.92520000000002</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="61" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="94">
-        <f>[2]Лист2!J41</f>
+      <c r="B6" s="62">
+        <f>Лист2!J41/1000000</f>
         <v>0</v>
       </c>
-      <c r="C6" s="94">
-        <f>[2]Лист2!J84</f>
+      <c r="C6" s="62">
+        <f>Лист2!J84</f>
         <v>0.15</v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="62">
         <f t="shared" si="0"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="E6" s="94">
+      <c r="E6" s="62">
         <v>0.5</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="B7" s="94">
-        <f>[2]Лист2!J43</f>
-        <v>230523</v>
-      </c>
-      <c r="C7" s="94">
-        <f>[2]Лист2!J74</f>
+      <c r="B7" s="62">
+        <f>Лист2!J43/1000000</f>
+        <v>1.2448242</v>
+      </c>
+      <c r="C7" s="62">
+        <f>Лист2!J74</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D7" s="94">
+      <c r="D7" s="62">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="E7" s="94">
+      <c r="E7" s="62">
         <v>2.5</v>
       </c>
-      <c r="F7" s="94">
+      <c r="F7" s="62">
         <f t="shared" si="1"/>
-        <v>115261500</v>
+        <v>622.41210000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="93" t="s">
+      <c r="A8" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="94">
-        <f>[2]Лист2!J45</f>
-        <v>12375</v>
-      </c>
-      <c r="C8" s="94">
-        <f>[2]Лист2!J69</f>
+      <c r="B8" s="62">
+        <f>Лист2!J45/1000000</f>
+        <v>6.6824999999999996E-2</v>
+      </c>
+      <c r="C8" s="62">
+        <f>Лист2!J69</f>
         <v>0.05</v>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="62">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E8" s="94">
+      <c r="E8" s="62">
         <v>2.5</v>
       </c>
-      <c r="F8" s="94">
+      <c r="F8" s="62">
         <f t="shared" si="1"/>
-        <v>618750</v>
+        <v>3.3412500000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="94">
-        <f>[2]Лист2!J47</f>
-        <v>376.68</v>
-      </c>
-      <c r="C9" s="94">
-        <f>[2]Лист2!J85</f>
+      <c r="B9" s="62">
+        <f>Лист2!J47/1000000</f>
+        <v>2.0340720000000001E-3</v>
+      </c>
+      <c r="C9" s="62">
+        <f>Лист2!J85</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="62">
         <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="62">
         <v>1</v>
       </c>
-      <c r="F9" s="94">
+      <c r="F9" s="62">
         <f t="shared" si="1"/>
-        <v>6278.0000000000009</v>
+        <v>3.3901200000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="B10" s="97">
-        <f>[2]Лист2!J49</f>
-        <v>1.5767999999999999E-3</v>
-      </c>
-      <c r="C10" s="98">
-        <f>[2]Лист2!J81</f>
+      <c r="B10" s="65">
+        <f>Лист2!J49/1000000</f>
+        <v>8.5147200000000006E-9</v>
+      </c>
+      <c r="C10" s="66">
+        <f>Лист2!J81</f>
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D10" s="97">
+      <c r="D10" s="65">
         <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="E10" s="99">
+      <c r="E10" s="67">
         <v>2.5</v>
       </c>
-      <c r="F10" s="94">
+      <c r="F10" s="62">
         <f t="shared" si="1"/>
-        <v>3942</v>
+        <v>2.1286799999999998E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="68" t="s">
         <v>229</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="103">
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="71">
         <f>SUM(F2:F10)</f>
-        <v>181530055.75</v>
+        <v>980.26230104999991</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="124" t="s">
+      <c r="A13" s="77" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="125">
+      <c r="B13" s="78">
         <v>2.4</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="C13" s="78" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="125">
+      <c r="B14" s="78">
         <v>1.68</v>
       </c>
-      <c r="C14" s="125"/>
+      <c r="C14" s="78"/>
     </row>
     <row r="15" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="77" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="125">
+      <c r="B15" s="78">
         <f>B13*B14*F11</f>
-        <v>731929184.78400004</v>
-      </c>
-      <c r="C15" s="125" t="s">
+        <v>3952.4175978335998</v>
+      </c>
+      <c r="C15" s="78" t="s">
         <v>233</v>
       </c>
     </row>
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="6:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="147" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="149"/>
+    </row>
+    <row r="18" spans="6:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F18" s="150"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="152"/>
+    </row>
+    <row r="19" spans="6:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="153" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" s="154"/>
+      <c r="H19" s="154"/>
+      <c r="I19" s="155"/>
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F20" s="156"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="157"/>
+      <c r="I20" s="158"/>
+    </row>
+    <row r="21" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F21" s="156"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="157"/>
+      <c r="I21" s="158"/>
+    </row>
+    <row r="22" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F22" s="156"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="158"/>
+    </row>
+    <row r="23" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="158"/>
+    </row>
+    <row r="24" spans="6:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="159"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="160"/>
+      <c r="I24" s="161"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F17:I18"/>
+    <mergeCell ref="F19:I24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>